--- a/Cell data Sara A549/2026_02_04/2026_02_04.xlsx
+++ b/Cell data Sara A549/2026_02_04/2026_02_04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara A549\2026_02_04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3113F1B1-F62A-4420-8141-264DA005D62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6384A99-8DF2-4FB1-BFBF-4A35EDA504AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="10">
   <si>
-    <t>Radiation</t>
-  </si>
-  <si>
     <t>Experiment</t>
   </si>
   <si>
@@ -39,13 +36,7 @@
     <t>Dose</t>
   </si>
   <si>
-    <t>Flask_number</t>
-  </si>
-  <si>
     <t>Cells plated</t>
-  </si>
-  <si>
-    <t>Colonies</t>
   </si>
   <si>
     <t>X-ray</t>
@@ -55,6 +46,15 @@
   </si>
   <si>
     <t>Proton HL</t>
+  </si>
+  <si>
+    <t>Rad</t>
+  </si>
+  <si>
+    <t>Triplicate</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
@@ -538,8 +538,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
@@ -866,1060 +865,1060 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
+      <c r="G1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <v>300</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="1">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <v>300</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>300</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4">
         <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5" s="1">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>300</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5">
         <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>0</v>
       </c>
-      <c r="E6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
         <v>300</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7" s="1">
-        <v>6</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
         <v>300</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7">
         <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
         <v>1.7</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>600</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
         <v>1.7</v>
       </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
         <v>600</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
         <v>1.7</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>600</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10">
         <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
         <v>4.25</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>2000</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
         <v>4.25</v>
       </c>
-      <c r="E12" s="1">
-        <v>2</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
         <v>2000</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12">
         <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
         <v>4.25</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>3</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13">
         <v>2000</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1">
-        <v>4</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
         <v>6.8</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14">
         <v>4000</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1">
-        <v>4</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
         <v>6.8</v>
       </c>
-      <c r="E15" s="1">
-        <v>2</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
         <v>4000</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1">
-        <v>4</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
         <v>6.8</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>3</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16">
         <v>4000</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>1.3</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>300</v>
+      </c>
+      <c r="G17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>1.3</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>300</v>
+      </c>
+      <c r="G18">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>1.3</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>300</v>
+      </c>
+      <c r="G19">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>1.3</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>300</v>
+      </c>
+      <c r="G20">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1.3</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>300</v>
+      </c>
+      <c r="G21">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>1.3</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22">
+        <v>300</v>
+      </c>
+      <c r="G22">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>1.3</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>600</v>
+      </c>
+      <c r="G23">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>1.3</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>600</v>
+      </c>
+      <c r="G24">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>1.3</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>600</v>
+      </c>
+      <c r="G25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>1.3</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>2000</v>
+      </c>
+      <c r="G26">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>1.3</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>2000</v>
+      </c>
+      <c r="G27">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>1.3</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>2000</v>
+      </c>
+      <c r="G28">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1.3</v>
+      </c>
+      <c r="D29">
         <v>8</v>
       </c>
-      <c r="B17" s="1">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>5000</v>
+      </c>
+      <c r="G29">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
         <v>1.3</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>5000</v>
+      </c>
+      <c r="G30">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>1.3</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+      <c r="F31">
+        <v>5000</v>
+      </c>
+      <c r="G31">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32">
+        <v>16.5</v>
+      </c>
+      <c r="D32">
         <v>0</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E32">
         <v>1</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F32">
         <v>300</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G32">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33">
+        <v>16.5</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>300</v>
+      </c>
+      <c r="G33">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>16.5</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34">
+        <v>300</v>
+      </c>
+      <c r="G34">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>16.5</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35">
+        <v>300</v>
+      </c>
+      <c r="G35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>16.5</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>5</v>
+      </c>
+      <c r="F36">
+        <v>300</v>
+      </c>
+      <c r="G36">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>16.5</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>6</v>
+      </c>
+      <c r="F37">
+        <v>300</v>
+      </c>
+      <c r="G37">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>16.5</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>600</v>
+      </c>
+      <c r="G38">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>16.5</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <v>600</v>
+      </c>
+      <c r="G39">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>16.5</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40">
+        <v>600</v>
+      </c>
+      <c r="G40">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>16.5</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>2000</v>
+      </c>
+      <c r="G41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42">
+        <v>16.5</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42">
+        <v>2000</v>
+      </c>
+      <c r="G42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>16.5</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>3</v>
+      </c>
+      <c r="F43">
+        <v>2000</v>
+      </c>
+      <c r="G43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44">
+        <v>16.5</v>
+      </c>
+      <c r="D44">
         <v>8</v>
       </c>
-      <c r="B18" s="1">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>5000</v>
+      </c>
+      <c r="G44">
         <v>0</v>
       </c>
-      <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="F18" s="1">
-        <v>300</v>
-      </c>
-      <c r="G18" s="1">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45">
+        <v>16.5</v>
+      </c>
+      <c r="D45">
         <v>8</v>
       </c>
-      <c r="B19" s="1">
-        <v>4</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45">
+        <v>5000</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+      <c r="C46">
+        <v>16.5</v>
+      </c>
+      <c r="D46">
+        <v>8</v>
+      </c>
+      <c r="E46">
         <v>3</v>
       </c>
-      <c r="F19" s="1">
-        <v>300</v>
-      </c>
-      <c r="G19" s="1">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="1">
-        <v>4</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1">
-        <v>4</v>
-      </c>
-      <c r="F20" s="1">
-        <v>300</v>
-      </c>
-      <c r="G20" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="1">
-        <v>4</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>5</v>
-      </c>
-      <c r="F21" s="1">
-        <v>300</v>
-      </c>
-      <c r="G21" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="1">
-        <v>4</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1">
-        <v>6</v>
-      </c>
-      <c r="F22" s="1">
-        <v>300</v>
-      </c>
-      <c r="G22" s="1">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="1">
-        <v>4</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>600</v>
-      </c>
-      <c r="G23" s="1">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="1">
-        <v>4</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2</v>
-      </c>
-      <c r="F24" s="1">
-        <v>600</v>
-      </c>
-      <c r="G24" s="1">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="1">
-        <v>4</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1">
-        <v>3</v>
-      </c>
-      <c r="F25" s="1">
-        <v>600</v>
-      </c>
-      <c r="G25" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="1">
-        <v>4</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D26" s="1">
-        <v>5</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G26" s="1">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="1">
-        <v>4</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D27" s="1">
-        <v>5</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G27" s="1">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D28" s="1">
-        <v>5</v>
-      </c>
-      <c r="E28" s="1">
-        <v>3</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G28" s="1">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="1">
-        <v>4</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D29" s="1">
-        <v>8</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
+      <c r="F46">
         <v>5000</v>
       </c>
-      <c r="G29" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="1">
-        <v>4</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D30" s="1">
-        <v>8</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2</v>
-      </c>
-      <c r="F30" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G30" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="1">
-        <v>4</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D31" s="1">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1">
-        <v>3</v>
-      </c>
-      <c r="F31" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G31" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="1">
-        <v>4</v>
-      </c>
-      <c r="C32" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>300</v>
-      </c>
-      <c r="G32" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="1">
-        <v>4</v>
-      </c>
-      <c r="C33" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1">
-        <v>2</v>
-      </c>
-      <c r="F33" s="1">
-        <v>300</v>
-      </c>
-      <c r="G33" s="1">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="1">
-        <v>4</v>
-      </c>
-      <c r="C34" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0</v>
-      </c>
-      <c r="E34" s="1">
-        <v>3</v>
-      </c>
-      <c r="F34" s="1">
-        <v>300</v>
-      </c>
-      <c r="G34" s="1">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="1">
-        <v>4</v>
-      </c>
-      <c r="C35" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0</v>
-      </c>
-      <c r="E35" s="1">
-        <v>4</v>
-      </c>
-      <c r="F35" s="1">
-        <v>300</v>
-      </c>
-      <c r="G35" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="1">
-        <v>4</v>
-      </c>
-      <c r="C36" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0</v>
-      </c>
-      <c r="E36" s="1">
-        <v>5</v>
-      </c>
-      <c r="F36" s="1">
-        <v>300</v>
-      </c>
-      <c r="G36" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="1">
-        <v>4</v>
-      </c>
-      <c r="C37" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
-        <v>6</v>
-      </c>
-      <c r="F37" s="1">
-        <v>300</v>
-      </c>
-      <c r="G37" s="1">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="1">
-        <v>4</v>
-      </c>
-      <c r="C38" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D38" s="1">
-        <v>2</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>600</v>
-      </c>
-      <c r="G38" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="1">
-        <v>4</v>
-      </c>
-      <c r="C39" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D39" s="1">
-        <v>2</v>
-      </c>
-      <c r="E39" s="1">
-        <v>2</v>
-      </c>
-      <c r="F39" s="1">
-        <v>600</v>
-      </c>
-      <c r="G39" s="1">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" s="1">
-        <v>4</v>
-      </c>
-      <c r="C40" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D40" s="1">
-        <v>2</v>
-      </c>
-      <c r="E40" s="1">
-        <v>3</v>
-      </c>
-      <c r="F40" s="1">
-        <v>600</v>
-      </c>
-      <c r="G40" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="1">
-        <v>4</v>
-      </c>
-      <c r="C41" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D41" s="1">
-        <v>5</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G41" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="1">
-        <v>4</v>
-      </c>
-      <c r="C42" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D42" s="1">
-        <v>5</v>
-      </c>
-      <c r="E42" s="1">
-        <v>2</v>
-      </c>
-      <c r="F42" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G42" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="1">
-        <v>4</v>
-      </c>
-      <c r="C43" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D43" s="1">
-        <v>5</v>
-      </c>
-      <c r="E43" s="1">
-        <v>3</v>
-      </c>
-      <c r="F43" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G43" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" s="1">
-        <v>4</v>
-      </c>
-      <c r="C44" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D44" s="1">
-        <v>8</v>
-      </c>
-      <c r="E44" s="1">
-        <v>1</v>
-      </c>
-      <c r="F44" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="1">
-        <v>4</v>
-      </c>
-      <c r="C45" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D45" s="1">
-        <v>8</v>
-      </c>
-      <c r="E45" s="1">
-        <v>2</v>
-      </c>
-      <c r="F45" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="1">
-        <v>4</v>
-      </c>
-      <c r="C46" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D46" s="1">
-        <v>8</v>
-      </c>
-      <c r="E46" s="1">
-        <v>3</v>
-      </c>
-      <c r="F46" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G46" s="1">
+      <c r="G46">
         <v>1</v>
       </c>
     </row>

--- a/Cell data Sara A549/2026_02_04/2026_02_04.xlsx
+++ b/Cell data Sara A549/2026_02_04/2026_02_04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara A549\2026_02_04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6384A99-8DF2-4FB1-BFBF-4A35EDA504AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDDAF25-FE05-4DD1-9100-987B196B91E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="11">
   <si>
     <t>Experiment</t>
   </si>
@@ -39,15 +39,6 @@
     <t>Cells plated</t>
   </si>
   <si>
-    <t>X-ray</t>
-  </si>
-  <si>
-    <t>Proton LL</t>
-  </si>
-  <si>
-    <t>Proton HL</t>
-  </si>
-  <si>
     <t>Rad</t>
   </si>
   <si>
@@ -55,6 +46,18 @@
   </si>
   <si>
     <t>Count</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Proton L</t>
+  </si>
+  <si>
+    <t>Proton H</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -861,12 +864,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -878,18 +881,18 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -912,7 +915,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -935,7 +938,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -958,7 +961,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -981,7 +984,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -1004,7 +1007,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -1027,7 +1030,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1050,7 +1053,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -1073,7 +1076,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -1096,7 +1099,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -1142,7 +1145,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -1165,7 +1168,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -1188,7 +1191,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -1211,7 +1214,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -1234,7 +1237,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -1257,7 +1260,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -1280,7 +1283,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -1303,7 +1306,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1326,7 +1329,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -1349,7 +1352,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -1372,7 +1375,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -1395,7 +1398,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -1418,7 +1421,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -1441,7 +1444,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -1464,7 +1467,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B27">
         <v>4</v>
@@ -1487,7 +1490,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B28">
         <v>4</v>
@@ -1510,7 +1513,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -1533,7 +1536,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -1556,7 +1559,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -1579,7 +1582,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B32">
         <v>4</v>
@@ -1588,21 +1591,21 @@
         <v>16.5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G32">
-        <v>70</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B33">
         <v>4</v>
@@ -1611,21 +1614,21 @@
         <v>16.5</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G33">
-        <v>74</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>4</v>
@@ -1634,21 +1637,21 @@
         <v>16.5</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G34">
-        <v>81</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -1657,21 +1660,21 @@
         <v>16.5</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G35">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1680,21 +1683,21 @@
         <v>16.5</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G36">
-        <v>73</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -1703,21 +1706,21 @@
         <v>16.5</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E37">
+        <v>3</v>
+      </c>
+      <c r="F37">
+        <v>2000</v>
+      </c>
+      <c r="G37">
         <v>6</v>
-      </c>
-      <c r="F37">
-        <v>300</v>
-      </c>
-      <c r="G37">
-        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B38">
         <v>4</v>
@@ -1726,21 +1729,21 @@
         <v>16.5</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>600</v>
+        <v>5000</v>
       </c>
       <c r="G38">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -1749,21 +1752,21 @@
         <v>16.5</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39">
-        <v>600</v>
+        <v>5000</v>
       </c>
       <c r="G39">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -1772,153 +1775,15 @@
         <v>16.5</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40">
-        <v>600</v>
+        <v>5000</v>
       </c>
       <c r="G40">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41">
-        <v>4</v>
-      </c>
-      <c r="C41">
-        <v>16.5</v>
-      </c>
-      <c r="D41">
-        <v>5</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>2000</v>
-      </c>
-      <c r="G41">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42">
-        <v>4</v>
-      </c>
-      <c r="C42">
-        <v>16.5</v>
-      </c>
-      <c r="D42">
-        <v>5</v>
-      </c>
-      <c r="E42">
-        <v>2</v>
-      </c>
-      <c r="F42">
-        <v>2000</v>
-      </c>
-      <c r="G42">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43">
-        <v>4</v>
-      </c>
-      <c r="C43">
-        <v>16.5</v>
-      </c>
-      <c r="D43">
-        <v>5</v>
-      </c>
-      <c r="E43">
-        <v>3</v>
-      </c>
-      <c r="F43">
-        <v>2000</v>
-      </c>
-      <c r="G43">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44">
-        <v>4</v>
-      </c>
-      <c r="C44">
-        <v>16.5</v>
-      </c>
-      <c r="D44">
-        <v>8</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>5000</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45">
-        <v>4</v>
-      </c>
-      <c r="C45">
-        <v>16.5</v>
-      </c>
-      <c r="D45">
-        <v>8</v>
-      </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45">
-        <v>5000</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46">
-        <v>4</v>
-      </c>
-      <c r="C46">
-        <v>16.5</v>
-      </c>
-      <c r="D46">
-        <v>8</v>
-      </c>
-      <c r="E46">
-        <v>3</v>
-      </c>
-      <c r="F46">
-        <v>5000</v>
-      </c>
-      <c r="G46">
         <v>1</v>
       </c>
     </row>

--- a/Cell data Sara A549/2026_02_04/2026_02_04.xlsx
+++ b/Cell data Sara A549/2026_02_04/2026_02_04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara A549\2026_02_04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDDAF25-FE05-4DD1-9100-987B196B91E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2D2FC7-6692-4477-8BC2-825093AAAEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1085,7 +1085,7 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1131,7 +1131,7 @@
         <v>2</v>
       </c>
       <c r="D12">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1154,7 +1154,7 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1177,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1223,7 +1223,7 @@
         <v>2</v>
       </c>
       <c r="D16">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>3</v>
